--- a/data/workbooks/2017_1.xlsx
+++ b/data/workbooks/2017_1.xlsx
@@ -3,15 +3,15 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E712B61-BA55-4CF7-9FB1-F6E1C61708E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{403A19AB-F803-4B14-AEF2-98DBE1665192}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Январь 2017" sheetId="53" r:id="rId1"/>
-    <sheet name="Февраль 2017" sheetId="54" r:id="rId2"/>
-    <sheet name="Март 2017 " sheetId="56" r:id="rId3"/>
-    <sheet name="Апрель 2017" sheetId="57" r:id="rId4"/>
+    <sheet name="Січень 2017" sheetId="53" r:id="rId1"/>
+    <sheet name="Лютий 2017" sheetId="54" r:id="rId2"/>
+    <sheet name="Березень 2017 " sheetId="56" r:id="rId3"/>
+    <sheet name="Квітень 2017" sheetId="57" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,39 +29,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="31">
-  <si>
-    <t>Доходы</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="32">
   <si>
     <t>Зарплата</t>
-  </si>
-  <si>
-    <t>Расходы</t>
-  </si>
-  <si>
-    <t>Потребности</t>
-  </si>
-  <si>
-    <t>Развлечения</t>
   </si>
   <si>
     <t>Квартира</t>
   </si>
   <si>
-    <t>Проезд</t>
-  </si>
-  <si>
-    <t>Другое</t>
-  </si>
-  <si>
     <t>Алкоголь</t>
-  </si>
-  <si>
-    <t>Всего</t>
-  </si>
-  <si>
-    <t>вс</t>
   </si>
   <si>
     <t>сб</t>
@@ -82,46 +58,73 @@
     <t>пн</t>
   </si>
   <si>
-    <t>Всего за месяц</t>
-  </si>
-  <si>
     <t>%</t>
-  </si>
-  <si>
-    <t>Прибыль</t>
-  </si>
-  <si>
-    <t>Здоровье</t>
-  </si>
-  <si>
-    <t>Хоз.Товары</t>
-  </si>
-  <si>
-    <t>В среднем</t>
-  </si>
-  <si>
-    <t>Питание</t>
-  </si>
-  <si>
-    <t>Другие доходы</t>
-  </si>
-  <si>
-    <t>Баланс на нач. мес.</t>
-  </si>
-  <si>
-    <t>Баланс на кон. мес.</t>
-  </si>
-  <si>
-    <t>Мероприятия</t>
   </si>
   <si>
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t>Вещи</t>
+    <t>Доходи</t>
   </si>
   <si>
-    <t>Закуски</t>
+    <t>Інші доходи</t>
+  </si>
+  <si>
+    <t>Витрати</t>
+  </si>
+  <si>
+    <t>Потреби</t>
+  </si>
+  <si>
+    <t>Харчування</t>
+  </si>
+  <si>
+    <t>Проїзд</t>
+  </si>
+  <si>
+    <t>Здоров'я</t>
+  </si>
+  <si>
+    <t>Госп.Товари</t>
+  </si>
+  <si>
+    <t>Речі та взуття</t>
+  </si>
+  <si>
+    <t>Інші витрати</t>
+  </si>
+  <si>
+    <t>Необов'язкове</t>
+  </si>
+  <si>
+    <t>Смаколики</t>
+  </si>
+  <si>
+    <t>Заходи</t>
+  </si>
+  <si>
+    <t>Розваги</t>
+  </si>
+  <si>
+    <t>Всього</t>
+  </si>
+  <si>
+    <t>Баланс на поч. міс.</t>
+  </si>
+  <si>
+    <t>Прибуток</t>
+  </si>
+  <si>
+    <t>Баланс на кін. міс.</t>
+  </si>
+  <si>
+    <t>нд</t>
+  </si>
+  <si>
+    <t>В середньому</t>
+  </si>
+  <si>
+    <t>Всього за місяць</t>
   </si>
 </sst>
 </file>
@@ -441,7 +444,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="113">
+  <cellXfs count="110">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -613,23 +616,73 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -662,12 +715,6 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -695,64 +742,13 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1106,123 +1102,123 @@
     <col min="2" max="2" width="6.140625" style="1" customWidth="1"/>
     <col min="3" max="3" width="19.28515625" style="1" customWidth="1"/>
     <col min="4" max="34" width="5.7109375" style="1" customWidth="1"/>
-    <col min="35" max="35" width="8.85546875" style="1" customWidth="1"/>
+    <col min="35" max="35" width="11.5703125" style="1" customWidth="1"/>
     <col min="36" max="36" width="10.140625" style="1" customWidth="1"/>
     <col min="37" max="37" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="95"/>
-      <c r="B1" s="95"/>
-      <c r="C1" s="96"/>
+      <c r="A1" s="70"/>
+      <c r="B1" s="70"/>
+      <c r="C1" s="71"/>
       <c r="D1" s="37" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="E1" s="55" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F1" s="36" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="G1" s="37" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="H1" s="36" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="I1" s="36" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="J1" s="36" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="K1" s="37" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="L1" s="55" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="M1" s="36" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="N1" s="37" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="O1" s="36" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="P1" s="36" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="Q1" s="36" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="R1" s="37" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="S1" s="55" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="T1" s="36" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="U1" s="37" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="V1" s="36" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="W1" s="36" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="X1" s="36" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="Y1" s="37" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="Z1" s="55" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="AA1" s="36" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="AB1" s="37" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="AC1" s="36" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="AD1" s="36" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="AE1" s="36" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="AF1" s="37" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="AG1" s="55" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="AH1" s="36" t="s">
-        <v>15</v>
-      </c>
-      <c r="AI1" s="99" t="s">
-        <v>22</v>
-      </c>
-      <c r="AJ1" s="101" t="s">
-        <v>17</v>
-      </c>
-      <c r="AK1" s="103" t="s">
-        <v>18</v>
+        <v>7</v>
+      </c>
+      <c r="AI1" s="74" t="s">
+        <v>30</v>
+      </c>
+      <c r="AJ1" s="76" t="s">
+        <v>31</v>
+      </c>
+      <c r="AK1" s="78" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="97"/>
-      <c r="B2" s="97"/>
-      <c r="C2" s="98"/>
+      <c r="A2" s="72"/>
+      <c r="B2" s="72"/>
+      <c r="C2" s="73"/>
       <c r="D2" s="11">
         <v>1</v>
       </c>
@@ -1316,17 +1312,17 @@
       <c r="AH2" s="12">
         <v>31</v>
       </c>
-      <c r="AI2" s="100"/>
-      <c r="AJ2" s="102"/>
-      <c r="AK2" s="104"/>
+      <c r="AI2" s="75"/>
+      <c r="AJ2" s="77"/>
+      <c r="AK2" s="79"/>
     </row>
     <row r="3" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="105" t="s">
+      <c r="A3" s="80" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="81"/>
+      <c r="C3" s="57" t="s">
         <v>0</v>
-      </c>
-      <c r="B3" s="106"/>
-      <c r="C3" s="57" t="s">
-        <v>1</v>
       </c>
       <c r="D3" s="14"/>
       <c r="E3" s="15"/>
@@ -1363,7 +1359,7 @@
       <c r="AF3" s="15"/>
       <c r="AG3" s="17"/>
       <c r="AH3" s="15"/>
-      <c r="AI3" s="109">
+      <c r="AI3" s="84">
         <f>(AJ3+AJ4)/31</f>
         <v>129.41935483870967</v>
       </c>
@@ -1371,15 +1367,15 @@
         <f>SUM(D3:AH3)</f>
         <v>3828</v>
       </c>
-      <c r="AK3" s="111">
+      <c r="AK3" s="86">
         <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="107"/>
-      <c r="B4" s="108"/>
+      <c r="A4" s="82"/>
+      <c r="B4" s="83"/>
       <c r="C4" s="58" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="D4" s="18"/>
       <c r="E4" s="18"/>
@@ -1416,22 +1412,22 @@
       <c r="AH4" s="18">
         <v>137</v>
       </c>
-      <c r="AI4" s="110"/>
+      <c r="AI4" s="85"/>
       <c r="AJ4" s="48">
         <f>SUM(D4:AH4)</f>
         <v>184</v>
       </c>
-      <c r="AK4" s="112"/>
+      <c r="AK4" s="87"/>
     </row>
     <row r="5" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="89" t="s">
-        <v>2</v>
-      </c>
-      <c r="B5" s="92" t="s">
-        <v>3</v>
+      <c r="A5" s="103" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="106" t="s">
+        <v>14</v>
       </c>
       <c r="C5" s="59" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
@@ -1518,10 +1514,10 @@
       </c>
     </row>
     <row r="6" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="90"/>
-      <c r="B6" s="92"/>
+      <c r="A6" s="104"/>
+      <c r="B6" s="106"/>
       <c r="C6" s="60" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4">
@@ -1606,10 +1602,10 @@
       </c>
     </row>
     <row r="7" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="90"/>
-      <c r="B7" s="92"/>
+      <c r="A7" s="104"/>
+      <c r="B7" s="106"/>
       <c r="C7" s="60" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
@@ -1658,10 +1654,10 @@
       </c>
     </row>
     <row r="8" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="90"/>
-      <c r="B8" s="92"/>
+      <c r="A8" s="104"/>
+      <c r="B8" s="106"/>
       <c r="C8" s="61" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D8" s="39"/>
       <c r="E8" s="39"/>
@@ -1714,10 +1710,10 @@
       </c>
     </row>
     <row r="9" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="90"/>
-      <c r="B9" s="92"/>
+      <c r="A9" s="104"/>
+      <c r="B9" s="106"/>
       <c r="C9" s="59" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
@@ -1770,10 +1766,10 @@
       </c>
     </row>
     <row r="10" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="90"/>
-      <c r="B10" s="92"/>
+      <c r="A10" s="104"/>
+      <c r="B10" s="106"/>
       <c r="C10" s="60" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
@@ -1822,10 +1818,10 @@
       </c>
     </row>
     <row r="11" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="90"/>
-      <c r="B11" s="92"/>
+      <c r="A11" s="104"/>
+      <c r="B11" s="106"/>
       <c r="C11" s="60" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
@@ -1878,12 +1874,12 @@
       </c>
     </row>
     <row r="12" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="90"/>
-      <c r="B12" s="93" t="s">
-        <v>4</v>
+      <c r="A12" s="104"/>
+      <c r="B12" s="107" t="s">
+        <v>21</v>
       </c>
       <c r="C12" s="62" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D12" s="6"/>
       <c r="E12" s="6"/>
@@ -1936,10 +1932,10 @@
       </c>
     </row>
     <row r="13" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="90"/>
-      <c r="B13" s="94"/>
+      <c r="A13" s="104"/>
+      <c r="B13" s="108"/>
       <c r="C13" s="62" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="D13" s="8"/>
       <c r="E13" s="8"/>
@@ -1990,10 +1986,10 @@
       </c>
     </row>
     <row r="14" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="90"/>
-      <c r="B14" s="94"/>
+      <c r="A14" s="104"/>
+      <c r="B14" s="108"/>
       <c r="C14" s="56" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D14" s="6"/>
       <c r="E14" s="6">
@@ -2054,10 +2050,10 @@
       </c>
     </row>
     <row r="15" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="90"/>
-      <c r="B15" s="94"/>
-      <c r="C15" s="65" t="s">
-        <v>4</v>
+      <c r="A15" s="104"/>
+      <c r="B15" s="108"/>
+      <c r="C15" s="62" t="s">
+        <v>24</v>
       </c>
       <c r="D15" s="51"/>
       <c r="E15" s="51">
@@ -2120,52 +2116,52 @@
       </c>
     </row>
     <row r="16" spans="1:37" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="91"/>
-      <c r="B16" s="66" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="63"/>
-      <c r="D16" s="68"/>
-      <c r="E16" s="78">
+      <c r="A16" s="105"/>
+      <c r="B16" s="94" t="s">
+        <v>25</v>
+      </c>
+      <c r="C16" s="95"/>
+      <c r="D16" s="66"/>
+      <c r="E16" s="94">
         <f>SUM(E5:K15)</f>
         <v>599</v>
       </c>
-      <c r="F16" s="79"/>
-      <c r="G16" s="79"/>
-      <c r="H16" s="79"/>
-      <c r="I16" s="79"/>
-      <c r="J16" s="79"/>
-      <c r="K16" s="80"/>
-      <c r="L16" s="78">
+      <c r="F16" s="95"/>
+      <c r="G16" s="95"/>
+      <c r="H16" s="95"/>
+      <c r="I16" s="95"/>
+      <c r="J16" s="95"/>
+      <c r="K16" s="96"/>
+      <c r="L16" s="94">
         <f>SUM(L5:R15)</f>
         <v>572</v>
       </c>
-      <c r="M16" s="79"/>
-      <c r="N16" s="79"/>
-      <c r="O16" s="79"/>
-      <c r="P16" s="79"/>
-      <c r="Q16" s="79"/>
-      <c r="R16" s="80"/>
-      <c r="S16" s="78">
+      <c r="M16" s="95"/>
+      <c r="N16" s="95"/>
+      <c r="O16" s="95"/>
+      <c r="P16" s="95"/>
+      <c r="Q16" s="95"/>
+      <c r="R16" s="96"/>
+      <c r="S16" s="94">
         <f>SUM(S5:Y15)</f>
         <v>1173</v>
       </c>
-      <c r="T16" s="79"/>
-      <c r="U16" s="79"/>
-      <c r="V16" s="79"/>
-      <c r="W16" s="79"/>
-      <c r="X16" s="79"/>
-      <c r="Y16" s="80"/>
-      <c r="Z16" s="78">
+      <c r="T16" s="95"/>
+      <c r="U16" s="95"/>
+      <c r="V16" s="95"/>
+      <c r="W16" s="95"/>
+      <c r="X16" s="95"/>
+      <c r="Y16" s="96"/>
+      <c r="Z16" s="94">
         <f>SUM(Z5:AF15)</f>
         <v>848</v>
       </c>
-      <c r="AA16" s="79"/>
-      <c r="AB16" s="79"/>
-      <c r="AC16" s="79"/>
-      <c r="AD16" s="79"/>
-      <c r="AE16" s="79"/>
-      <c r="AF16" s="80"/>
+      <c r="AA16" s="95"/>
+      <c r="AB16" s="95"/>
+      <c r="AC16" s="95"/>
+      <c r="AD16" s="95"/>
+      <c r="AE16" s="95"/>
+      <c r="AF16" s="96"/>
       <c r="AG16" s="63"/>
       <c r="AH16" s="64"/>
       <c r="AI16" s="53">
@@ -2182,153 +2178,146 @@
       </c>
     </row>
     <row r="17" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="81" t="s">
-        <v>25</v>
-      </c>
-      <c r="B17" s="82"/>
-      <c r="C17" s="83"/>
-      <c r="D17" s="84">
+      <c r="A17" s="97" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17" s="97"/>
+      <c r="C17" s="109"/>
+      <c r="D17" s="98">
         <v>10654</v>
       </c>
-      <c r="E17" s="85"/>
-      <c r="F17" s="85"/>
-      <c r="G17" s="85"/>
-      <c r="H17" s="85"/>
-      <c r="I17" s="85"/>
-      <c r="J17" s="85"/>
-      <c r="K17" s="85"/>
-      <c r="L17" s="85"/>
-      <c r="M17" s="85"/>
-      <c r="N17" s="85"/>
-      <c r="O17" s="85"/>
-      <c r="P17" s="85"/>
-      <c r="Q17" s="85"/>
-      <c r="R17" s="85"/>
-      <c r="S17" s="85"/>
-      <c r="T17" s="85"/>
-      <c r="U17" s="85"/>
-      <c r="V17" s="85"/>
-      <c r="W17" s="85"/>
-      <c r="X17" s="85"/>
-      <c r="Y17" s="85"/>
-      <c r="Z17" s="85"/>
-      <c r="AA17" s="85"/>
-      <c r="AB17" s="85"/>
-      <c r="AC17" s="85"/>
-      <c r="AD17" s="85"/>
-      <c r="AE17" s="85"/>
-      <c r="AF17" s="85"/>
-      <c r="AG17" s="85"/>
-      <c r="AH17" s="85"/>
-      <c r="AI17" s="86"/>
-      <c r="AJ17" s="87"/>
-      <c r="AK17" s="67"/>
+      <c r="E17" s="99"/>
+      <c r="F17" s="99"/>
+      <c r="G17" s="99"/>
+      <c r="H17" s="99"/>
+      <c r="I17" s="99"/>
+      <c r="J17" s="99"/>
+      <c r="K17" s="99"/>
+      <c r="L17" s="99"/>
+      <c r="M17" s="99"/>
+      <c r="N17" s="99"/>
+      <c r="O17" s="99"/>
+      <c r="P17" s="99"/>
+      <c r="Q17" s="99"/>
+      <c r="R17" s="99"/>
+      <c r="S17" s="99"/>
+      <c r="T17" s="99"/>
+      <c r="U17" s="99"/>
+      <c r="V17" s="99"/>
+      <c r="W17" s="99"/>
+      <c r="X17" s="99"/>
+      <c r="Y17" s="99"/>
+      <c r="Z17" s="99"/>
+      <c r="AA17" s="99"/>
+      <c r="AB17" s="99"/>
+      <c r="AC17" s="99"/>
+      <c r="AD17" s="99"/>
+      <c r="AE17" s="99"/>
+      <c r="AF17" s="99"/>
+      <c r="AG17" s="99"/>
+      <c r="AH17" s="99"/>
+      <c r="AI17" s="100"/>
+      <c r="AJ17" s="101"/>
+      <c r="AK17" s="65"/>
     </row>
     <row r="18" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="73" t="s">
-        <v>19</v>
-      </c>
-      <c r="B18" s="73"/>
-      <c r="C18" s="74"/>
-      <c r="D18" s="88">
+      <c r="A18" s="89" t="s">
+        <v>27</v>
+      </c>
+      <c r="B18" s="89"/>
+      <c r="C18" s="90"/>
+      <c r="D18" s="102">
         <f>(AJ3+AJ4)-AJ16</f>
         <v>408</v>
       </c>
-      <c r="E18" s="86"/>
-      <c r="F18" s="86"/>
-      <c r="G18" s="86"/>
-      <c r="H18" s="86"/>
-      <c r="I18" s="86"/>
-      <c r="J18" s="86"/>
-      <c r="K18" s="86"/>
-      <c r="L18" s="86"/>
-      <c r="M18" s="86"/>
-      <c r="N18" s="86"/>
-      <c r="O18" s="86"/>
-      <c r="P18" s="86"/>
-      <c r="Q18" s="86"/>
-      <c r="R18" s="86"/>
-      <c r="S18" s="86"/>
-      <c r="T18" s="86"/>
-      <c r="U18" s="86"/>
-      <c r="V18" s="86"/>
-      <c r="W18" s="86"/>
-      <c r="X18" s="86"/>
-      <c r="Y18" s="86"/>
-      <c r="Z18" s="86"/>
-      <c r="AA18" s="86"/>
-      <c r="AB18" s="86"/>
-      <c r="AC18" s="86"/>
-      <c r="AD18" s="86"/>
-      <c r="AE18" s="86"/>
-      <c r="AF18" s="86"/>
-      <c r="AG18" s="86"/>
-      <c r="AH18" s="86"/>
-      <c r="AI18" s="86"/>
-      <c r="AJ18" s="87"/>
+      <c r="E18" s="100"/>
+      <c r="F18" s="100"/>
+      <c r="G18" s="100"/>
+      <c r="H18" s="100"/>
+      <c r="I18" s="100"/>
+      <c r="J18" s="100"/>
+      <c r="K18" s="100"/>
+      <c r="L18" s="100"/>
+      <c r="M18" s="100"/>
+      <c r="N18" s="100"/>
+      <c r="O18" s="100"/>
+      <c r="P18" s="100"/>
+      <c r="Q18" s="100"/>
+      <c r="R18" s="100"/>
+      <c r="S18" s="100"/>
+      <c r="T18" s="100"/>
+      <c r="U18" s="100"/>
+      <c r="V18" s="100"/>
+      <c r="W18" s="100"/>
+      <c r="X18" s="100"/>
+      <c r="Y18" s="100"/>
+      <c r="Z18" s="100"/>
+      <c r="AA18" s="100"/>
+      <c r="AB18" s="100"/>
+      <c r="AC18" s="100"/>
+      <c r="AD18" s="100"/>
+      <c r="AE18" s="100"/>
+      <c r="AF18" s="100"/>
+      <c r="AG18" s="100"/>
+      <c r="AH18" s="100"/>
+      <c r="AI18" s="100"/>
+      <c r="AJ18" s="101"/>
       <c r="AK18" s="31">
         <f>((AJ3+AJ4-AJ16)/(AJ3+AJ4))*100</f>
         <v>10.16949152542373</v>
       </c>
     </row>
     <row r="19" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="72" t="s">
-        <v>26</v>
-      </c>
-      <c r="B19" s="73"/>
-      <c r="C19" s="74"/>
-      <c r="D19" s="75">
+      <c r="A19" s="88" t="s">
+        <v>28</v>
+      </c>
+      <c r="B19" s="89"/>
+      <c r="C19" s="90"/>
+      <c r="D19" s="91">
         <f>(AJ3+AJ4+D17)-AJ16</f>
         <v>11062</v>
       </c>
-      <c r="E19" s="76"/>
-      <c r="F19" s="76"/>
-      <c r="G19" s="76"/>
-      <c r="H19" s="76"/>
-      <c r="I19" s="76"/>
-      <c r="J19" s="76"/>
-      <c r="K19" s="76"/>
-      <c r="L19" s="76"/>
-      <c r="M19" s="76"/>
-      <c r="N19" s="76"/>
-      <c r="O19" s="76"/>
-      <c r="P19" s="76"/>
-      <c r="Q19" s="76"/>
-      <c r="R19" s="76"/>
-      <c r="S19" s="76"/>
-      <c r="T19" s="76"/>
-      <c r="U19" s="76"/>
-      <c r="V19" s="76"/>
-      <c r="W19" s="76"/>
-      <c r="X19" s="76"/>
-      <c r="Y19" s="76"/>
-      <c r="Z19" s="76"/>
-      <c r="AA19" s="76"/>
-      <c r="AB19" s="76"/>
-      <c r="AC19" s="76"/>
-      <c r="AD19" s="76"/>
-      <c r="AE19" s="76"/>
-      <c r="AF19" s="76"/>
-      <c r="AG19" s="76"/>
-      <c r="AH19" s="76"/>
-      <c r="AI19" s="76"/>
-      <c r="AJ19" s="77"/>
+      <c r="E19" s="92"/>
+      <c r="F19" s="92"/>
+      <c r="G19" s="92"/>
+      <c r="H19" s="92"/>
+      <c r="I19" s="92"/>
+      <c r="J19" s="92"/>
+      <c r="K19" s="92"/>
+      <c r="L19" s="92"/>
+      <c r="M19" s="92"/>
+      <c r="N19" s="92"/>
+      <c r="O19" s="92"/>
+      <c r="P19" s="92"/>
+      <c r="Q19" s="92"/>
+      <c r="R19" s="92"/>
+      <c r="S19" s="92"/>
+      <c r="T19" s="92"/>
+      <c r="U19" s="92"/>
+      <c r="V19" s="92"/>
+      <c r="W19" s="92"/>
+      <c r="X19" s="92"/>
+      <c r="Y19" s="92"/>
+      <c r="Z19" s="92"/>
+      <c r="AA19" s="92"/>
+      <c r="AB19" s="92"/>
+      <c r="AC19" s="92"/>
+      <c r="AD19" s="92"/>
+      <c r="AE19" s="92"/>
+      <c r="AF19" s="92"/>
+      <c r="AG19" s="92"/>
+      <c r="AH19" s="92"/>
+      <c r="AI19" s="92"/>
+      <c r="AJ19" s="93"/>
       <c r="AK19" s="54"/>
     </row>
     <row r="24" spans="1:37" x14ac:dyDescent="0.3">
       <c r="S24" s="1" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="20">
-    <mergeCell ref="A1:C2"/>
-    <mergeCell ref="AI1:AI2"/>
-    <mergeCell ref="AJ1:AJ2"/>
-    <mergeCell ref="AK1:AK2"/>
-    <mergeCell ref="A3:B4"/>
-    <mergeCell ref="AI3:AI4"/>
-    <mergeCell ref="AK3:AK4"/>
+  <mergeCells count="21">
     <mergeCell ref="A19:C19"/>
     <mergeCell ref="D19:AJ19"/>
     <mergeCell ref="E16:K16"/>
@@ -2342,6 +2331,14 @@
     <mergeCell ref="A5:A16"/>
     <mergeCell ref="B5:B11"/>
     <mergeCell ref="B12:B15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="A1:C2"/>
+    <mergeCell ref="AI1:AI2"/>
+    <mergeCell ref="AJ1:AJ2"/>
+    <mergeCell ref="AK1:AK2"/>
+    <mergeCell ref="A3:B4"/>
+    <mergeCell ref="AI3:AI4"/>
+    <mergeCell ref="AK3:AK4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2357,117 +2354,117 @@
     <col min="2" max="2" width="6.140625" style="1" customWidth="1"/>
     <col min="3" max="3" width="19.28515625" style="1" customWidth="1"/>
     <col min="4" max="34" width="5.7109375" style="1" customWidth="1"/>
-    <col min="35" max="35" width="8.85546875" style="1" customWidth="1"/>
+    <col min="35" max="35" width="11.85546875" style="1" customWidth="1"/>
     <col min="36" max="36" width="10.140625" style="1" customWidth="1"/>
     <col min="37" max="37" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="95"/>
-      <c r="B1" s="95"/>
-      <c r="C1" s="96"/>
+      <c r="A1" s="70"/>
+      <c r="B1" s="70"/>
+      <c r="C1" s="71"/>
       <c r="D1" s="37" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E1" s="36" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="F1" s="36" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="G1" s="36" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="H1" s="37" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="I1" s="55" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="J1" s="36" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="K1" s="37" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="L1" s="36" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="M1" s="36" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="N1" s="36" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="O1" s="37" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="P1" s="55" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="Q1" s="36" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="R1" s="37" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="S1" s="36" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T1" s="36" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="U1" s="36" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="V1" s="37" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="W1" s="55" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="X1" s="36" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="Y1" s="37" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="Z1" s="36" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="AA1" s="36" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="AB1" s="36" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="AC1" s="37" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="AD1" s="55" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="AE1" s="36" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="AF1" s="37"/>
       <c r="AG1" s="36"/>
       <c r="AH1" s="36"/>
-      <c r="AI1" s="99" t="s">
-        <v>22</v>
-      </c>
-      <c r="AJ1" s="101" t="s">
-        <v>17</v>
-      </c>
-      <c r="AK1" s="103" t="s">
-        <v>18</v>
+      <c r="AI1" s="74" t="s">
+        <v>30</v>
+      </c>
+      <c r="AJ1" s="76" t="s">
+        <v>31</v>
+      </c>
+      <c r="AK1" s="78" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="97"/>
-      <c r="B2" s="97"/>
-      <c r="C2" s="98"/>
+      <c r="A2" s="72"/>
+      <c r="B2" s="72"/>
+      <c r="C2" s="73"/>
       <c r="D2" s="11">
         <v>1</v>
       </c>
@@ -2561,17 +2558,17 @@
       <c r="AH2" s="12">
         <v>31</v>
       </c>
-      <c r="AI2" s="100"/>
-      <c r="AJ2" s="102"/>
-      <c r="AK2" s="104"/>
+      <c r="AI2" s="75"/>
+      <c r="AJ2" s="77"/>
+      <c r="AK2" s="79"/>
     </row>
     <row r="3" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="105" t="s">
+      <c r="A3" s="80" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="81"/>
+      <c r="C3" s="57" t="s">
         <v>0</v>
-      </c>
-      <c r="B3" s="106"/>
-      <c r="C3" s="57" t="s">
-        <v>1</v>
       </c>
       <c r="D3" s="14"/>
       <c r="E3" s="15"/>
@@ -2610,7 +2607,7 @@
       <c r="AF3" s="15"/>
       <c r="AG3" s="17"/>
       <c r="AH3" s="15"/>
-      <c r="AI3" s="109">
+      <c r="AI3" s="84">
         <f>(AJ3+AJ4)/31</f>
         <v>155.83870967741936</v>
       </c>
@@ -2618,15 +2615,15 @@
         <f>SUM(D3:AH3)</f>
         <v>4831</v>
       </c>
-      <c r="AK3" s="111">
+      <c r="AK3" s="86">
         <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="107"/>
-      <c r="B4" s="108"/>
+      <c r="A4" s="82"/>
+      <c r="B4" s="83"/>
       <c r="C4" s="58" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="D4" s="18"/>
       <c r="E4" s="18"/>
@@ -2659,22 +2656,22 @@
       <c r="AF4" s="18"/>
       <c r="AG4" s="19"/>
       <c r="AH4" s="18"/>
-      <c r="AI4" s="110"/>
+      <c r="AI4" s="85"/>
       <c r="AJ4" s="48">
         <f>SUM(D4:AH4)</f>
         <v>0</v>
       </c>
-      <c r="AK4" s="112"/>
+      <c r="AK4" s="87"/>
     </row>
     <row r="5" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="89" t="s">
-        <v>2</v>
-      </c>
-      <c r="B5" s="92" t="s">
-        <v>3</v>
+      <c r="A5" s="103" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="106" t="s">
+        <v>14</v>
       </c>
       <c r="C5" s="59" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="D5" s="2">
         <v>13</v>
@@ -2753,10 +2750,10 @@
       </c>
     </row>
     <row r="6" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="90"/>
-      <c r="B6" s="92"/>
+      <c r="A6" s="104"/>
+      <c r="B6" s="106"/>
       <c r="C6" s="60" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D6" s="4">
         <v>7</v>
@@ -2827,10 +2824,10 @@
       </c>
     </row>
     <row r="7" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="90"/>
-      <c r="B7" s="92"/>
+      <c r="A7" s="104"/>
+      <c r="B7" s="106"/>
       <c r="C7" s="60" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D7" s="4">
         <v>13</v>
@@ -2881,10 +2878,10 @@
       </c>
     </row>
     <row r="8" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="90"/>
-      <c r="B8" s="92"/>
+      <c r="A8" s="104"/>
+      <c r="B8" s="106"/>
       <c r="C8" s="61" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D8" s="39"/>
       <c r="E8" s="39"/>
@@ -2941,10 +2938,10 @@
       </c>
     </row>
     <row r="9" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="90"/>
-      <c r="B9" s="92"/>
+      <c r="A9" s="104"/>
+      <c r="B9" s="106"/>
       <c r="C9" s="59" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
@@ -2993,10 +2990,10 @@
       </c>
     </row>
     <row r="10" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="90"/>
-      <c r="B10" s="92"/>
+      <c r="A10" s="104"/>
+      <c r="B10" s="106"/>
       <c r="C10" s="60" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
@@ -3043,10 +3040,10 @@
       </c>
     </row>
     <row r="11" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="90"/>
-      <c r="B11" s="92"/>
+      <c r="A11" s="104"/>
+      <c r="B11" s="106"/>
       <c r="C11" s="60" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
@@ -3097,12 +3094,12 @@
       </c>
     </row>
     <row r="12" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="90"/>
-      <c r="B12" s="93" t="s">
-        <v>4</v>
+      <c r="A12" s="104"/>
+      <c r="B12" s="107" t="s">
+        <v>21</v>
       </c>
       <c r="C12" s="62" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D12" s="6"/>
       <c r="E12" s="6"/>
@@ -3157,10 +3154,10 @@
       </c>
     </row>
     <row r="13" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="90"/>
-      <c r="B13" s="94"/>
+      <c r="A13" s="104"/>
+      <c r="B13" s="108"/>
       <c r="C13" s="62" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="D13" s="8"/>
       <c r="E13" s="8"/>
@@ -3213,10 +3210,10 @@
       </c>
     </row>
     <row r="14" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="90"/>
-      <c r="B14" s="94"/>
+      <c r="A14" s="104"/>
+      <c r="B14" s="108"/>
       <c r="C14" s="56" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D14" s="6"/>
       <c r="E14" s="6"/>
@@ -3273,10 +3270,10 @@
       </c>
     </row>
     <row r="15" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="90"/>
-      <c r="B15" s="94"/>
-      <c r="C15" s="65" t="s">
-        <v>4</v>
+      <c r="A15" s="104"/>
+      <c r="B15" s="108"/>
+      <c r="C15" s="62" t="s">
+        <v>24</v>
       </c>
       <c r="D15" s="51"/>
       <c r="E15" s="51"/>
@@ -3337,54 +3334,54 @@
       </c>
     </row>
     <row r="16" spans="1:37" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="91"/>
-      <c r="B16" s="66" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="63"/>
-      <c r="D16" s="78">
+      <c r="A16" s="105"/>
+      <c r="B16" s="94" t="s">
+        <v>25</v>
+      </c>
+      <c r="C16" s="95"/>
+      <c r="D16" s="94">
         <f>SUM(D5:H15)</f>
         <v>922</v>
       </c>
-      <c r="E16" s="79"/>
-      <c r="F16" s="79"/>
-      <c r="G16" s="79"/>
-      <c r="H16" s="80"/>
-      <c r="I16" s="78">
+      <c r="E16" s="95"/>
+      <c r="F16" s="95"/>
+      <c r="G16" s="95"/>
+      <c r="H16" s="96"/>
+      <c r="I16" s="94">
         <f>SUM(I5:O15)</f>
         <v>1246</v>
       </c>
-      <c r="J16" s="79"/>
-      <c r="K16" s="79"/>
-      <c r="L16" s="79"/>
-      <c r="M16" s="79"/>
-      <c r="N16" s="79"/>
-      <c r="O16" s="80"/>
-      <c r="P16" s="78">
+      <c r="J16" s="95"/>
+      <c r="K16" s="95"/>
+      <c r="L16" s="95"/>
+      <c r="M16" s="95"/>
+      <c r="N16" s="95"/>
+      <c r="O16" s="96"/>
+      <c r="P16" s="94">
         <f>SUM(P5:V15)</f>
         <v>1305</v>
       </c>
-      <c r="Q16" s="79"/>
-      <c r="R16" s="79"/>
-      <c r="S16" s="79"/>
-      <c r="T16" s="79"/>
-      <c r="U16" s="79"/>
-      <c r="V16" s="80"/>
-      <c r="W16" s="78">
+      <c r="Q16" s="95"/>
+      <c r="R16" s="95"/>
+      <c r="S16" s="95"/>
+      <c r="T16" s="95"/>
+      <c r="U16" s="95"/>
+      <c r="V16" s="96"/>
+      <c r="W16" s="94">
         <f>SUM(W5:AC15)</f>
         <v>549</v>
       </c>
-      <c r="X16" s="79"/>
-      <c r="Y16" s="79"/>
-      <c r="Z16" s="79"/>
-      <c r="AA16" s="79"/>
-      <c r="AB16" s="79"/>
-      <c r="AC16" s="80"/>
-      <c r="AD16" s="78">
+      <c r="X16" s="95"/>
+      <c r="Y16" s="95"/>
+      <c r="Z16" s="95"/>
+      <c r="AA16" s="95"/>
+      <c r="AB16" s="95"/>
+      <c r="AC16" s="96"/>
+      <c r="AD16" s="94">
         <f>SUM(AD5:AE15)</f>
         <v>30</v>
       </c>
-      <c r="AE16" s="80"/>
+      <c r="AE16" s="96"/>
       <c r="AF16" s="63"/>
       <c r="AG16" s="63"/>
       <c r="AH16" s="64"/>
@@ -3402,153 +3399,146 @@
       </c>
     </row>
     <row r="17" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="81" t="s">
-        <v>25</v>
-      </c>
-      <c r="B17" s="82"/>
-      <c r="C17" s="83"/>
-      <c r="D17" s="84">
+      <c r="A17" s="97" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17" s="97"/>
+      <c r="C17" s="109"/>
+      <c r="D17" s="98">
         <v>11062</v>
       </c>
-      <c r="E17" s="85"/>
-      <c r="F17" s="85"/>
-      <c r="G17" s="85"/>
-      <c r="H17" s="85"/>
-      <c r="I17" s="85"/>
-      <c r="J17" s="85"/>
-      <c r="K17" s="85"/>
-      <c r="L17" s="85"/>
-      <c r="M17" s="85"/>
-      <c r="N17" s="85"/>
-      <c r="O17" s="85"/>
-      <c r="P17" s="85"/>
-      <c r="Q17" s="85"/>
-      <c r="R17" s="85"/>
-      <c r="S17" s="85"/>
-      <c r="T17" s="85"/>
-      <c r="U17" s="85"/>
-      <c r="V17" s="85"/>
-      <c r="W17" s="85"/>
-      <c r="X17" s="85"/>
-      <c r="Y17" s="85"/>
-      <c r="Z17" s="85"/>
-      <c r="AA17" s="85"/>
-      <c r="AB17" s="85"/>
-      <c r="AC17" s="85"/>
-      <c r="AD17" s="85"/>
-      <c r="AE17" s="85"/>
-      <c r="AF17" s="85"/>
-      <c r="AG17" s="85"/>
-      <c r="AH17" s="85"/>
-      <c r="AI17" s="86"/>
-      <c r="AJ17" s="87"/>
-      <c r="AK17" s="69"/>
+      <c r="E17" s="99"/>
+      <c r="F17" s="99"/>
+      <c r="G17" s="99"/>
+      <c r="H17" s="99"/>
+      <c r="I17" s="99"/>
+      <c r="J17" s="99"/>
+      <c r="K17" s="99"/>
+      <c r="L17" s="99"/>
+      <c r="M17" s="99"/>
+      <c r="N17" s="99"/>
+      <c r="O17" s="99"/>
+      <c r="P17" s="99"/>
+      <c r="Q17" s="99"/>
+      <c r="R17" s="99"/>
+      <c r="S17" s="99"/>
+      <c r="T17" s="99"/>
+      <c r="U17" s="99"/>
+      <c r="V17" s="99"/>
+      <c r="W17" s="99"/>
+      <c r="X17" s="99"/>
+      <c r="Y17" s="99"/>
+      <c r="Z17" s="99"/>
+      <c r="AA17" s="99"/>
+      <c r="AB17" s="99"/>
+      <c r="AC17" s="99"/>
+      <c r="AD17" s="99"/>
+      <c r="AE17" s="99"/>
+      <c r="AF17" s="99"/>
+      <c r="AG17" s="99"/>
+      <c r="AH17" s="99"/>
+      <c r="AI17" s="100"/>
+      <c r="AJ17" s="101"/>
+      <c r="AK17" s="67"/>
     </row>
     <row r="18" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="73" t="s">
-        <v>19</v>
-      </c>
-      <c r="B18" s="73"/>
-      <c r="C18" s="74"/>
-      <c r="D18" s="88">
+      <c r="A18" s="89" t="s">
+        <v>27</v>
+      </c>
+      <c r="B18" s="89"/>
+      <c r="C18" s="90"/>
+      <c r="D18" s="102">
         <f>(AJ3+AJ4)-AJ16</f>
         <v>779</v>
       </c>
-      <c r="E18" s="86"/>
-      <c r="F18" s="86"/>
-      <c r="G18" s="86"/>
-      <c r="H18" s="86"/>
-      <c r="I18" s="86"/>
-      <c r="J18" s="86"/>
-      <c r="K18" s="86"/>
-      <c r="L18" s="86"/>
-      <c r="M18" s="86"/>
-      <c r="N18" s="86"/>
-      <c r="O18" s="86"/>
-      <c r="P18" s="86"/>
-      <c r="Q18" s="86"/>
-      <c r="R18" s="86"/>
-      <c r="S18" s="86"/>
-      <c r="T18" s="86"/>
-      <c r="U18" s="86"/>
-      <c r="V18" s="86"/>
-      <c r="W18" s="86"/>
-      <c r="X18" s="86"/>
-      <c r="Y18" s="86"/>
-      <c r="Z18" s="86"/>
-      <c r="AA18" s="86"/>
-      <c r="AB18" s="86"/>
-      <c r="AC18" s="86"/>
-      <c r="AD18" s="86"/>
-      <c r="AE18" s="86"/>
-      <c r="AF18" s="86"/>
-      <c r="AG18" s="86"/>
-      <c r="AH18" s="86"/>
-      <c r="AI18" s="86"/>
-      <c r="AJ18" s="87"/>
+      <c r="E18" s="100"/>
+      <c r="F18" s="100"/>
+      <c r="G18" s="100"/>
+      <c r="H18" s="100"/>
+      <c r="I18" s="100"/>
+      <c r="J18" s="100"/>
+      <c r="K18" s="100"/>
+      <c r="L18" s="100"/>
+      <c r="M18" s="100"/>
+      <c r="N18" s="100"/>
+      <c r="O18" s="100"/>
+      <c r="P18" s="100"/>
+      <c r="Q18" s="100"/>
+      <c r="R18" s="100"/>
+      <c r="S18" s="100"/>
+      <c r="T18" s="100"/>
+      <c r="U18" s="100"/>
+      <c r="V18" s="100"/>
+      <c r="W18" s="100"/>
+      <c r="X18" s="100"/>
+      <c r="Y18" s="100"/>
+      <c r="Z18" s="100"/>
+      <c r="AA18" s="100"/>
+      <c r="AB18" s="100"/>
+      <c r="AC18" s="100"/>
+      <c r="AD18" s="100"/>
+      <c r="AE18" s="100"/>
+      <c r="AF18" s="100"/>
+      <c r="AG18" s="100"/>
+      <c r="AH18" s="100"/>
+      <c r="AI18" s="100"/>
+      <c r="AJ18" s="101"/>
       <c r="AK18" s="31">
         <f>((AJ3+AJ4-AJ16)/(AJ3+AJ4))*100</f>
         <v>16.125025874560134</v>
       </c>
     </row>
     <row r="19" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="72" t="s">
-        <v>26</v>
-      </c>
-      <c r="B19" s="73"/>
-      <c r="C19" s="74"/>
-      <c r="D19" s="75">
+      <c r="A19" s="88" t="s">
+        <v>28</v>
+      </c>
+      <c r="B19" s="89"/>
+      <c r="C19" s="90"/>
+      <c r="D19" s="91">
         <f>(AJ3+AJ4+D17)-AJ16</f>
         <v>11841</v>
       </c>
-      <c r="E19" s="76"/>
-      <c r="F19" s="76"/>
-      <c r="G19" s="76"/>
-      <c r="H19" s="76"/>
-      <c r="I19" s="76"/>
-      <c r="J19" s="76"/>
-      <c r="K19" s="76"/>
-      <c r="L19" s="76"/>
-      <c r="M19" s="76"/>
-      <c r="N19" s="76"/>
-      <c r="O19" s="76"/>
-      <c r="P19" s="76"/>
-      <c r="Q19" s="76"/>
-      <c r="R19" s="76"/>
-      <c r="S19" s="76"/>
-      <c r="T19" s="76"/>
-      <c r="U19" s="76"/>
-      <c r="V19" s="76"/>
-      <c r="W19" s="76"/>
-      <c r="X19" s="76"/>
-      <c r="Y19" s="76"/>
-      <c r="Z19" s="76"/>
-      <c r="AA19" s="76"/>
-      <c r="AB19" s="76"/>
-      <c r="AC19" s="76"/>
-      <c r="AD19" s="76"/>
-      <c r="AE19" s="76"/>
-      <c r="AF19" s="76"/>
-      <c r="AG19" s="76"/>
-      <c r="AH19" s="76"/>
-      <c r="AI19" s="76"/>
-      <c r="AJ19" s="77"/>
+      <c r="E19" s="92"/>
+      <c r="F19" s="92"/>
+      <c r="G19" s="92"/>
+      <c r="H19" s="92"/>
+      <c r="I19" s="92"/>
+      <c r="J19" s="92"/>
+      <c r="K19" s="92"/>
+      <c r="L19" s="92"/>
+      <c r="M19" s="92"/>
+      <c r="N19" s="92"/>
+      <c r="O19" s="92"/>
+      <c r="P19" s="92"/>
+      <c r="Q19" s="92"/>
+      <c r="R19" s="92"/>
+      <c r="S19" s="92"/>
+      <c r="T19" s="92"/>
+      <c r="U19" s="92"/>
+      <c r="V19" s="92"/>
+      <c r="W19" s="92"/>
+      <c r="X19" s="92"/>
+      <c r="Y19" s="92"/>
+      <c r="Z19" s="92"/>
+      <c r="AA19" s="92"/>
+      <c r="AB19" s="92"/>
+      <c r="AC19" s="92"/>
+      <c r="AD19" s="92"/>
+      <c r="AE19" s="92"/>
+      <c r="AF19" s="92"/>
+      <c r="AG19" s="92"/>
+      <c r="AH19" s="92"/>
+      <c r="AI19" s="92"/>
+      <c r="AJ19" s="93"/>
       <c r="AK19" s="54"/>
     </row>
     <row r="24" spans="1:37" x14ac:dyDescent="0.3">
       <c r="S24" s="1" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="21">
-    <mergeCell ref="A1:C2"/>
-    <mergeCell ref="AI1:AI2"/>
-    <mergeCell ref="AJ1:AJ2"/>
-    <mergeCell ref="AK1:AK2"/>
-    <mergeCell ref="A3:B4"/>
-    <mergeCell ref="AI3:AI4"/>
-    <mergeCell ref="AK3:AK4"/>
+  <mergeCells count="22">
     <mergeCell ref="A19:C19"/>
     <mergeCell ref="D19:AJ19"/>
     <mergeCell ref="D16:H16"/>
@@ -3563,6 +3553,14 @@
     <mergeCell ref="D17:AJ17"/>
     <mergeCell ref="A18:C18"/>
     <mergeCell ref="D18:AJ18"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="A1:C2"/>
+    <mergeCell ref="AI1:AI2"/>
+    <mergeCell ref="AJ1:AJ2"/>
+    <mergeCell ref="AK1:AK2"/>
+    <mergeCell ref="A3:B4"/>
+    <mergeCell ref="AI3:AI4"/>
+    <mergeCell ref="AK3:AK4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3578,123 +3576,123 @@
     <col min="2" max="2" width="6.140625" style="1" customWidth="1"/>
     <col min="3" max="3" width="19.28515625" style="1" customWidth="1"/>
     <col min="4" max="34" width="5.7109375" style="1" customWidth="1"/>
-    <col min="35" max="35" width="8.85546875" style="1" customWidth="1"/>
+    <col min="35" max="35" width="12" style="1" customWidth="1"/>
     <col min="36" max="36" width="10.140625" style="1" customWidth="1"/>
     <col min="37" max="37" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="95"/>
-      <c r="B1" s="95"/>
-      <c r="C1" s="96"/>
+      <c r="A1" s="70"/>
+      <c r="B1" s="70"/>
+      <c r="C1" s="71"/>
       <c r="D1" s="37" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E1" s="36" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="F1" s="36" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="G1" s="36" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="H1" s="37" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="I1" s="55" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="J1" s="36" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="K1" s="37" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="L1" s="36" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="M1" s="36" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="N1" s="36" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="O1" s="37" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="P1" s="55" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="Q1" s="36" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="R1" s="37" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="S1" s="36" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T1" s="36" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="U1" s="36" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="V1" s="37" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="W1" s="55" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="X1" s="36" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="Y1" s="37" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="Z1" s="36" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="AA1" s="36" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="AB1" s="36" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="AC1" s="37" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="AD1" s="55" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="AE1" s="36" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="AF1" s="37" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="AG1" s="36" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="AH1" s="36" t="s">
-        <v>12</v>
-      </c>
-      <c r="AI1" s="99" t="s">
-        <v>22</v>
-      </c>
-      <c r="AJ1" s="101" t="s">
-        <v>17</v>
-      </c>
-      <c r="AK1" s="103" t="s">
-        <v>18</v>
+        <v>4</v>
+      </c>
+      <c r="AI1" s="74" t="s">
+        <v>30</v>
+      </c>
+      <c r="AJ1" s="76" t="s">
+        <v>31</v>
+      </c>
+      <c r="AK1" s="78" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="97"/>
-      <c r="B2" s="97"/>
-      <c r="C2" s="98"/>
+      <c r="A2" s="72"/>
+      <c r="B2" s="72"/>
+      <c r="C2" s="73"/>
       <c r="D2" s="11">
         <v>1</v>
       </c>
@@ -3788,17 +3786,17 @@
       <c r="AH2" s="12">
         <v>31</v>
       </c>
-      <c r="AI2" s="100"/>
-      <c r="AJ2" s="102"/>
-      <c r="AK2" s="104"/>
+      <c r="AI2" s="75"/>
+      <c r="AJ2" s="77"/>
+      <c r="AK2" s="79"/>
     </row>
     <row r="3" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="105" t="s">
+      <c r="A3" s="80" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="81"/>
+      <c r="C3" s="57" t="s">
         <v>0</v>
-      </c>
-      <c r="B3" s="106"/>
-      <c r="C3" s="57" t="s">
-        <v>1</v>
       </c>
       <c r="D3" s="14"/>
       <c r="E3" s="15"/>
@@ -3833,7 +3831,7 @@
       <c r="AF3" s="15"/>
       <c r="AG3" s="17"/>
       <c r="AH3" s="15"/>
-      <c r="AI3" s="109">
+      <c r="AI3" s="84">
         <f>(AJ3+AJ4)/31</f>
         <v>58.193548387096776</v>
       </c>
@@ -3841,15 +3839,15 @@
         <f>SUM(D3:AH3)</f>
         <v>1804</v>
       </c>
-      <c r="AK3" s="111">
+      <c r="AK3" s="86">
         <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="107"/>
-      <c r="B4" s="108"/>
+      <c r="A4" s="82"/>
+      <c r="B4" s="83"/>
       <c r="C4" s="58" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="D4" s="18"/>
       <c r="E4" s="18"/>
@@ -3882,22 +3880,22 @@
       <c r="AF4" s="18"/>
       <c r="AG4" s="19"/>
       <c r="AH4" s="18"/>
-      <c r="AI4" s="110"/>
+      <c r="AI4" s="85"/>
       <c r="AJ4" s="48">
         <f>SUM(D4:AH4)</f>
         <v>0</v>
       </c>
-      <c r="AK4" s="112"/>
+      <c r="AK4" s="87"/>
     </row>
     <row r="5" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="89" t="s">
-        <v>2</v>
-      </c>
-      <c r="B5" s="92" t="s">
-        <v>3</v>
+      <c r="A5" s="103" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="106" t="s">
+        <v>14</v>
       </c>
       <c r="C5" s="59" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="D5" s="2">
         <v>4</v>
@@ -3986,10 +3984,10 @@
       </c>
     </row>
     <row r="6" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="90"/>
-      <c r="B6" s="92"/>
+      <c r="A6" s="104"/>
+      <c r="B6" s="106"/>
       <c r="C6" s="60" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D6" s="4">
         <v>8</v>
@@ -4080,10 +4078,10 @@
       </c>
     </row>
     <row r="7" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="90"/>
-      <c r="B7" s="92"/>
+      <c r="A7" s="104"/>
+      <c r="B7" s="106"/>
       <c r="C7" s="60" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
@@ -4132,10 +4130,10 @@
       </c>
     </row>
     <row r="8" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="90"/>
-      <c r="B8" s="92"/>
+      <c r="A8" s="104"/>
+      <c r="B8" s="106"/>
       <c r="C8" s="61" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D8" s="39">
         <v>24</v>
@@ -4192,10 +4190,10 @@
       </c>
     </row>
     <row r="9" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="90"/>
-      <c r="B9" s="92"/>
+      <c r="A9" s="104"/>
+      <c r="B9" s="106"/>
       <c r="C9" s="59" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
@@ -4242,10 +4240,10 @@
       </c>
     </row>
     <row r="10" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="90"/>
-      <c r="B10" s="92"/>
+      <c r="A10" s="104"/>
+      <c r="B10" s="106"/>
       <c r="C10" s="60" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
@@ -4292,10 +4290,10 @@
       </c>
     </row>
     <row r="11" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="90"/>
-      <c r="B11" s="92"/>
+      <c r="A11" s="104"/>
+      <c r="B11" s="106"/>
       <c r="C11" s="60" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2">
@@ -4350,12 +4348,12 @@
       </c>
     </row>
     <row r="12" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="90"/>
-      <c r="B12" s="93" t="s">
-        <v>4</v>
+      <c r="A12" s="104"/>
+      <c r="B12" s="107" t="s">
+        <v>21</v>
       </c>
       <c r="C12" s="62" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D12" s="6"/>
       <c r="E12" s="6"/>
@@ -4410,10 +4408,10 @@
       </c>
     </row>
     <row r="13" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="90"/>
-      <c r="B13" s="94"/>
+      <c r="A13" s="104"/>
+      <c r="B13" s="108"/>
       <c r="C13" s="62" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="D13" s="8"/>
       <c r="E13" s="8"/>
@@ -4468,10 +4466,10 @@
       </c>
     </row>
     <row r="14" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="90"/>
-      <c r="B14" s="94"/>
+      <c r="A14" s="104"/>
+      <c r="B14" s="108"/>
       <c r="C14" s="56" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D14" s="6">
         <v>23</v>
@@ -4534,10 +4532,10 @@
       </c>
     </row>
     <row r="15" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="90"/>
-      <c r="B15" s="94"/>
-      <c r="C15" s="65" t="s">
-        <v>4</v>
+      <c r="A15" s="104"/>
+      <c r="B15" s="108"/>
+      <c r="C15" s="62" t="s">
+        <v>24</v>
       </c>
       <c r="D15" s="51"/>
       <c r="E15" s="51"/>
@@ -4596,57 +4594,57 @@
       </c>
     </row>
     <row r="16" spans="1:37" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="91"/>
-      <c r="B16" s="66" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="63"/>
-      <c r="D16" s="78">
+      <c r="A16" s="105"/>
+      <c r="B16" s="94" t="s">
+        <v>25</v>
+      </c>
+      <c r="C16" s="95"/>
+      <c r="D16" s="94">
         <f>SUM(D5:H15)+30</f>
         <v>486</v>
       </c>
-      <c r="E16" s="79"/>
-      <c r="F16" s="79"/>
-      <c r="G16" s="79"/>
-      <c r="H16" s="80"/>
-      <c r="I16" s="78">
+      <c r="E16" s="95"/>
+      <c r="F16" s="95"/>
+      <c r="G16" s="95"/>
+      <c r="H16" s="96"/>
+      <c r="I16" s="94">
         <f>SUM(I5:O15)</f>
         <v>804</v>
       </c>
-      <c r="J16" s="79"/>
-      <c r="K16" s="79"/>
-      <c r="L16" s="79"/>
-      <c r="M16" s="79"/>
-      <c r="N16" s="79"/>
-      <c r="O16" s="80"/>
-      <c r="P16" s="78">
+      <c r="J16" s="95"/>
+      <c r="K16" s="95"/>
+      <c r="L16" s="95"/>
+      <c r="M16" s="95"/>
+      <c r="N16" s="95"/>
+      <c r="O16" s="96"/>
+      <c r="P16" s="94">
         <f>SUM(P5:V15)</f>
         <v>1283</v>
       </c>
-      <c r="Q16" s="79"/>
-      <c r="R16" s="79"/>
-      <c r="S16" s="79"/>
-      <c r="T16" s="79"/>
-      <c r="U16" s="79"/>
-      <c r="V16" s="80"/>
-      <c r="W16" s="78">
+      <c r="Q16" s="95"/>
+      <c r="R16" s="95"/>
+      <c r="S16" s="95"/>
+      <c r="T16" s="95"/>
+      <c r="U16" s="95"/>
+      <c r="V16" s="96"/>
+      <c r="W16" s="94">
         <f>SUM(W5:AC15)</f>
         <v>553</v>
       </c>
-      <c r="X16" s="79"/>
-      <c r="Y16" s="79"/>
-      <c r="Z16" s="79"/>
-      <c r="AA16" s="79"/>
-      <c r="AB16" s="79"/>
-      <c r="AC16" s="80"/>
-      <c r="AD16" s="78">
+      <c r="X16" s="95"/>
+      <c r="Y16" s="95"/>
+      <c r="Z16" s="95"/>
+      <c r="AA16" s="95"/>
+      <c r="AB16" s="95"/>
+      <c r="AC16" s="96"/>
+      <c r="AD16" s="94">
         <f>SUM(AD5:AH15)</f>
         <v>754</v>
       </c>
-      <c r="AE16" s="79"/>
-      <c r="AF16" s="79"/>
-      <c r="AG16" s="79"/>
-      <c r="AH16" s="80"/>
+      <c r="AE16" s="95"/>
+      <c r="AF16" s="95"/>
+      <c r="AG16" s="95"/>
+      <c r="AH16" s="96"/>
       <c r="AI16" s="53">
         <f>AJ16/31</f>
         <v>124.19354838709677</v>
@@ -4661,153 +4659,146 @@
       </c>
     </row>
     <row r="17" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="81" t="s">
-        <v>25</v>
-      </c>
-      <c r="B17" s="82"/>
-      <c r="C17" s="83"/>
-      <c r="D17" s="84">
+      <c r="A17" s="97" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17" s="97"/>
+      <c r="C17" s="109"/>
+      <c r="D17" s="98">
         <v>11841</v>
       </c>
-      <c r="E17" s="85"/>
-      <c r="F17" s="85"/>
-      <c r="G17" s="85"/>
-      <c r="H17" s="85"/>
-      <c r="I17" s="85"/>
-      <c r="J17" s="85"/>
-      <c r="K17" s="85"/>
-      <c r="L17" s="85"/>
-      <c r="M17" s="85"/>
-      <c r="N17" s="85"/>
-      <c r="O17" s="85"/>
-      <c r="P17" s="85"/>
-      <c r="Q17" s="85"/>
-      <c r="R17" s="85"/>
-      <c r="S17" s="85"/>
-      <c r="T17" s="85"/>
-      <c r="U17" s="85"/>
-      <c r="V17" s="85"/>
-      <c r="W17" s="85"/>
-      <c r="X17" s="85"/>
-      <c r="Y17" s="85"/>
-      <c r="Z17" s="85"/>
-      <c r="AA17" s="85"/>
-      <c r="AB17" s="85"/>
-      <c r="AC17" s="85"/>
-      <c r="AD17" s="85"/>
-      <c r="AE17" s="85"/>
-      <c r="AF17" s="85"/>
-      <c r="AG17" s="85"/>
-      <c r="AH17" s="85"/>
-      <c r="AI17" s="86"/>
-      <c r="AJ17" s="87"/>
-      <c r="AK17" s="70"/>
+      <c r="E17" s="99"/>
+      <c r="F17" s="99"/>
+      <c r="G17" s="99"/>
+      <c r="H17" s="99"/>
+      <c r="I17" s="99"/>
+      <c r="J17" s="99"/>
+      <c r="K17" s="99"/>
+      <c r="L17" s="99"/>
+      <c r="M17" s="99"/>
+      <c r="N17" s="99"/>
+      <c r="O17" s="99"/>
+      <c r="P17" s="99"/>
+      <c r="Q17" s="99"/>
+      <c r="R17" s="99"/>
+      <c r="S17" s="99"/>
+      <c r="T17" s="99"/>
+      <c r="U17" s="99"/>
+      <c r="V17" s="99"/>
+      <c r="W17" s="99"/>
+      <c r="X17" s="99"/>
+      <c r="Y17" s="99"/>
+      <c r="Z17" s="99"/>
+      <c r="AA17" s="99"/>
+      <c r="AB17" s="99"/>
+      <c r="AC17" s="99"/>
+      <c r="AD17" s="99"/>
+      <c r="AE17" s="99"/>
+      <c r="AF17" s="99"/>
+      <c r="AG17" s="99"/>
+      <c r="AH17" s="99"/>
+      <c r="AI17" s="100"/>
+      <c r="AJ17" s="101"/>
+      <c r="AK17" s="68"/>
     </row>
     <row r="18" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="73" t="s">
-        <v>19</v>
-      </c>
-      <c r="B18" s="73"/>
-      <c r="C18" s="74"/>
-      <c r="D18" s="88">
+      <c r="A18" s="89" t="s">
+        <v>27</v>
+      </c>
+      <c r="B18" s="89"/>
+      <c r="C18" s="90"/>
+      <c r="D18" s="102">
         <f>(AJ3+AJ4)-AJ16</f>
         <v>-2046</v>
       </c>
-      <c r="E18" s="86"/>
-      <c r="F18" s="86"/>
-      <c r="G18" s="86"/>
-      <c r="H18" s="86"/>
-      <c r="I18" s="86"/>
-      <c r="J18" s="86"/>
-      <c r="K18" s="86"/>
-      <c r="L18" s="86"/>
-      <c r="M18" s="86"/>
-      <c r="N18" s="86"/>
-      <c r="O18" s="86"/>
-      <c r="P18" s="86"/>
-      <c r="Q18" s="86"/>
-      <c r="R18" s="86"/>
-      <c r="S18" s="86"/>
-      <c r="T18" s="86"/>
-      <c r="U18" s="86"/>
-      <c r="V18" s="86"/>
-      <c r="W18" s="86"/>
-      <c r="X18" s="86"/>
-      <c r="Y18" s="86"/>
-      <c r="Z18" s="86"/>
-      <c r="AA18" s="86"/>
-      <c r="AB18" s="86"/>
-      <c r="AC18" s="86"/>
-      <c r="AD18" s="86"/>
-      <c r="AE18" s="86"/>
-      <c r="AF18" s="86"/>
-      <c r="AG18" s="86"/>
-      <c r="AH18" s="86"/>
-      <c r="AI18" s="86"/>
-      <c r="AJ18" s="87"/>
+      <c r="E18" s="100"/>
+      <c r="F18" s="100"/>
+      <c r="G18" s="100"/>
+      <c r="H18" s="100"/>
+      <c r="I18" s="100"/>
+      <c r="J18" s="100"/>
+      <c r="K18" s="100"/>
+      <c r="L18" s="100"/>
+      <c r="M18" s="100"/>
+      <c r="N18" s="100"/>
+      <c r="O18" s="100"/>
+      <c r="P18" s="100"/>
+      <c r="Q18" s="100"/>
+      <c r="R18" s="100"/>
+      <c r="S18" s="100"/>
+      <c r="T18" s="100"/>
+      <c r="U18" s="100"/>
+      <c r="V18" s="100"/>
+      <c r="W18" s="100"/>
+      <c r="X18" s="100"/>
+      <c r="Y18" s="100"/>
+      <c r="Z18" s="100"/>
+      <c r="AA18" s="100"/>
+      <c r="AB18" s="100"/>
+      <c r="AC18" s="100"/>
+      <c r="AD18" s="100"/>
+      <c r="AE18" s="100"/>
+      <c r="AF18" s="100"/>
+      <c r="AG18" s="100"/>
+      <c r="AH18" s="100"/>
+      <c r="AI18" s="100"/>
+      <c r="AJ18" s="101"/>
       <c r="AK18" s="31">
         <f>((AJ3+AJ4-AJ16)/(AJ3+AJ4))*100</f>
         <v>-113.41463414634146</v>
       </c>
     </row>
     <row r="19" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="72" t="s">
-        <v>26</v>
-      </c>
-      <c r="B19" s="73"/>
-      <c r="C19" s="74"/>
-      <c r="D19" s="75">
+      <c r="A19" s="88" t="s">
+        <v>28</v>
+      </c>
+      <c r="B19" s="89"/>
+      <c r="C19" s="90"/>
+      <c r="D19" s="91">
         <f>(AJ3+AJ4+D17)-AJ16</f>
         <v>9795</v>
       </c>
-      <c r="E19" s="76"/>
-      <c r="F19" s="76"/>
-      <c r="G19" s="76"/>
-      <c r="H19" s="76"/>
-      <c r="I19" s="76"/>
-      <c r="J19" s="76"/>
-      <c r="K19" s="76"/>
-      <c r="L19" s="76"/>
-      <c r="M19" s="76"/>
-      <c r="N19" s="76"/>
-      <c r="O19" s="76"/>
-      <c r="P19" s="76"/>
-      <c r="Q19" s="76"/>
-      <c r="R19" s="76"/>
-      <c r="S19" s="76"/>
-      <c r="T19" s="76"/>
-      <c r="U19" s="76"/>
-      <c r="V19" s="76"/>
-      <c r="W19" s="76"/>
-      <c r="X19" s="76"/>
-      <c r="Y19" s="76"/>
-      <c r="Z19" s="76"/>
-      <c r="AA19" s="76"/>
-      <c r="AB19" s="76"/>
-      <c r="AC19" s="76"/>
-      <c r="AD19" s="76"/>
-      <c r="AE19" s="76"/>
-      <c r="AF19" s="76"/>
-      <c r="AG19" s="76"/>
-      <c r="AH19" s="76"/>
-      <c r="AI19" s="76"/>
-      <c r="AJ19" s="77"/>
+      <c r="E19" s="92"/>
+      <c r="F19" s="92"/>
+      <c r="G19" s="92"/>
+      <c r="H19" s="92"/>
+      <c r="I19" s="92"/>
+      <c r="J19" s="92"/>
+      <c r="K19" s="92"/>
+      <c r="L19" s="92"/>
+      <c r="M19" s="92"/>
+      <c r="N19" s="92"/>
+      <c r="O19" s="92"/>
+      <c r="P19" s="92"/>
+      <c r="Q19" s="92"/>
+      <c r="R19" s="92"/>
+      <c r="S19" s="92"/>
+      <c r="T19" s="92"/>
+      <c r="U19" s="92"/>
+      <c r="V19" s="92"/>
+      <c r="W19" s="92"/>
+      <c r="X19" s="92"/>
+      <c r="Y19" s="92"/>
+      <c r="Z19" s="92"/>
+      <c r="AA19" s="92"/>
+      <c r="AB19" s="92"/>
+      <c r="AC19" s="92"/>
+      <c r="AD19" s="92"/>
+      <c r="AE19" s="92"/>
+      <c r="AF19" s="92"/>
+      <c r="AG19" s="92"/>
+      <c r="AH19" s="92"/>
+      <c r="AI19" s="92"/>
+      <c r="AJ19" s="93"/>
       <c r="AK19" s="54"/>
     </row>
     <row r="24" spans="1:37" x14ac:dyDescent="0.3">
       <c r="S24" s="1" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="21">
-    <mergeCell ref="A1:C2"/>
-    <mergeCell ref="AI1:AI2"/>
-    <mergeCell ref="AJ1:AJ2"/>
-    <mergeCell ref="AK1:AK2"/>
-    <mergeCell ref="A3:B4"/>
-    <mergeCell ref="AI3:AI4"/>
-    <mergeCell ref="AK3:AK4"/>
+  <mergeCells count="22">
     <mergeCell ref="A19:C19"/>
     <mergeCell ref="D19:AJ19"/>
     <mergeCell ref="AD16:AH16"/>
@@ -4822,6 +4813,14 @@
     <mergeCell ref="D16:H16"/>
     <mergeCell ref="I16:O16"/>
     <mergeCell ref="P16:V16"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="A1:C2"/>
+    <mergeCell ref="AI1:AI2"/>
+    <mergeCell ref="AJ1:AJ2"/>
+    <mergeCell ref="AK1:AK2"/>
+    <mergeCell ref="A3:B4"/>
+    <mergeCell ref="AI3:AI4"/>
+    <mergeCell ref="AK3:AK4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -4837,121 +4836,121 @@
     <col min="2" max="2" width="6.140625" style="1" customWidth="1"/>
     <col min="3" max="3" width="19.28515625" style="1" customWidth="1"/>
     <col min="4" max="34" width="5.7109375" style="1" customWidth="1"/>
-    <col min="35" max="35" width="8.85546875" style="1" customWidth="1"/>
+    <col min="35" max="35" width="11.5703125" style="1" customWidth="1"/>
     <col min="36" max="36" width="10.140625" style="1" customWidth="1"/>
     <col min="37" max="37" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="95"/>
-      <c r="B1" s="95"/>
-      <c r="C1" s="96"/>
+      <c r="A1" s="70"/>
+      <c r="B1" s="70"/>
+      <c r="C1" s="71"/>
       <c r="D1" s="36" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E1" s="37" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="F1" s="55" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G1" s="36" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="H1" s="37" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="I1" s="36" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="J1" s="36" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="K1" s="36" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="L1" s="37" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="M1" s="55" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="N1" s="36" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="O1" s="37" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="P1" s="36" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="Q1" s="36" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="R1" s="36" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="S1" s="37" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="T1" s="55" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="U1" s="36" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="V1" s="37" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="W1" s="36" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="X1" s="36" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="Y1" s="36" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="Z1" s="37" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="AA1" s="55" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="AB1" s="36" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="AC1" s="37" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="AD1" s="36" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="AE1" s="36" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="AF1" s="36" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="AG1" s="37" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="AH1" s="36"/>
-      <c r="AI1" s="99" t="s">
-        <v>22</v>
-      </c>
-      <c r="AJ1" s="101" t="s">
-        <v>17</v>
-      </c>
-      <c r="AK1" s="103" t="s">
-        <v>18</v>
+      <c r="AI1" s="74" t="s">
+        <v>30</v>
+      </c>
+      <c r="AJ1" s="76" t="s">
+        <v>31</v>
+      </c>
+      <c r="AK1" s="78" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="97"/>
-      <c r="B2" s="97"/>
-      <c r="C2" s="98"/>
+      <c r="A2" s="72"/>
+      <c r="B2" s="72"/>
+      <c r="C2" s="73"/>
       <c r="D2" s="11">
         <v>1</v>
       </c>
@@ -5045,17 +5044,17 @@
       <c r="AH2" s="12">
         <v>31</v>
       </c>
-      <c r="AI2" s="100"/>
-      <c r="AJ2" s="102"/>
-      <c r="AK2" s="104"/>
+      <c r="AI2" s="75"/>
+      <c r="AJ2" s="77"/>
+      <c r="AK2" s="79"/>
     </row>
     <row r="3" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="105" t="s">
+      <c r="A3" s="80" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="81"/>
+      <c r="C3" s="57" t="s">
         <v>0</v>
-      </c>
-      <c r="B3" s="106"/>
-      <c r="C3" s="57" t="s">
-        <v>1</v>
       </c>
       <c r="D3" s="14"/>
       <c r="E3" s="15"/>
@@ -5088,7 +5087,7 @@
       <c r="AF3" s="15"/>
       <c r="AG3" s="17"/>
       <c r="AH3" s="15"/>
-      <c r="AI3" s="109">
+      <c r="AI3" s="84">
         <f>(AJ3+AJ4)/31</f>
         <v>16.129032258064516</v>
       </c>
@@ -5096,15 +5095,15 @@
         <f>SUM(D3:AH3)</f>
         <v>0</v>
       </c>
-      <c r="AK3" s="111">
+      <c r="AK3" s="86">
         <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="107"/>
-      <c r="B4" s="108"/>
+      <c r="A4" s="82"/>
+      <c r="B4" s="83"/>
       <c r="C4" s="58" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="D4" s="18"/>
       <c r="E4" s="18"/>
@@ -5139,22 +5138,22 @@
       </c>
       <c r="AG4" s="19"/>
       <c r="AH4" s="18"/>
-      <c r="AI4" s="110"/>
+      <c r="AI4" s="85"/>
       <c r="AJ4" s="48">
         <f>SUM(D4:AH4)</f>
         <v>500</v>
       </c>
-      <c r="AK4" s="112"/>
+      <c r="AK4" s="87"/>
     </row>
     <row r="5" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="89" t="s">
-        <v>2</v>
-      </c>
-      <c r="B5" s="92" t="s">
-        <v>3</v>
+      <c r="A5" s="103" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="106" t="s">
+        <v>14</v>
       </c>
       <c r="C5" s="59" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
@@ -5231,10 +5230,10 @@
       </c>
     </row>
     <row r="6" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="90"/>
-      <c r="B6" s="92"/>
+      <c r="A6" s="104"/>
+      <c r="B6" s="106"/>
       <c r="C6" s="60" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4">
@@ -5329,10 +5328,10 @@
       </c>
     </row>
     <row r="7" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="90"/>
-      <c r="B7" s="92"/>
+      <c r="A7" s="104"/>
+      <c r="B7" s="106"/>
       <c r="C7" s="60" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
@@ -5381,10 +5380,10 @@
       </c>
     </row>
     <row r="8" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="90"/>
-      <c r="B8" s="92"/>
+      <c r="A8" s="104"/>
+      <c r="B8" s="106"/>
       <c r="C8" s="61" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D8" s="39"/>
       <c r="E8" s="39"/>
@@ -5435,10 +5434,10 @@
       </c>
     </row>
     <row r="9" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="90"/>
-      <c r="B9" s="92"/>
+      <c r="A9" s="104"/>
+      <c r="B9" s="106"/>
       <c r="C9" s="59" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
@@ -5489,10 +5488,10 @@
       </c>
     </row>
     <row r="10" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="90"/>
-      <c r="B10" s="92"/>
+      <c r="A10" s="104"/>
+      <c r="B10" s="106"/>
       <c r="C10" s="60" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
@@ -5541,10 +5540,10 @@
       </c>
     </row>
     <row r="11" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="90"/>
-      <c r="B11" s="92"/>
+      <c r="A11" s="104"/>
+      <c r="B11" s="106"/>
       <c r="C11" s="60" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
@@ -5595,12 +5594,12 @@
       </c>
     </row>
     <row r="12" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="90"/>
-      <c r="B12" s="93" t="s">
-        <v>4</v>
+      <c r="A12" s="104"/>
+      <c r="B12" s="107" t="s">
+        <v>21</v>
       </c>
       <c r="C12" s="62" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D12" s="6"/>
       <c r="E12" s="6"/>
@@ -5651,10 +5650,10 @@
       </c>
     </row>
     <row r="13" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="90"/>
-      <c r="B13" s="94"/>
+      <c r="A13" s="104"/>
+      <c r="B13" s="108"/>
       <c r="C13" s="62" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="D13" s="8"/>
       <c r="E13" s="8"/>
@@ -5705,10 +5704,10 @@
       </c>
     </row>
     <row r="14" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="90"/>
-      <c r="B14" s="94"/>
+      <c r="A14" s="104"/>
+      <c r="B14" s="108"/>
       <c r="C14" s="56" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D14" s="6">
         <v>340</v>
@@ -5771,10 +5770,10 @@
       </c>
     </row>
     <row r="15" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="90"/>
-      <c r="B15" s="94"/>
-      <c r="C15" s="65" t="s">
-        <v>4</v>
+      <c r="A15" s="104"/>
+      <c r="B15" s="108"/>
+      <c r="C15" s="62" t="s">
+        <v>24</v>
       </c>
       <c r="D15" s="51"/>
       <c r="E15" s="51"/>
@@ -5831,56 +5830,56 @@
       </c>
     </row>
     <row r="16" spans="1:37" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="91"/>
-      <c r="B16" s="66" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="63"/>
-      <c r="D16" s="78">
+      <c r="A16" s="105"/>
+      <c r="B16" s="94" t="s">
+        <v>25</v>
+      </c>
+      <c r="C16" s="95"/>
+      <c r="D16" s="94">
         <f>SUM(D5:E15)+754</f>
         <v>1127</v>
       </c>
-      <c r="E16" s="80"/>
-      <c r="F16" s="78">
+      <c r="E16" s="96"/>
+      <c r="F16" s="94">
         <f>SUM(F5:L15)</f>
         <v>502</v>
       </c>
-      <c r="G16" s="79"/>
-      <c r="H16" s="79"/>
-      <c r="I16" s="79"/>
-      <c r="J16" s="79"/>
-      <c r="K16" s="79"/>
-      <c r="L16" s="80"/>
-      <c r="M16" s="78">
+      <c r="G16" s="95"/>
+      <c r="H16" s="95"/>
+      <c r="I16" s="95"/>
+      <c r="J16" s="95"/>
+      <c r="K16" s="95"/>
+      <c r="L16" s="96"/>
+      <c r="M16" s="94">
         <f>SUM(M5:S15)</f>
         <v>1099</v>
       </c>
-      <c r="N16" s="79"/>
-      <c r="O16" s="79"/>
-      <c r="P16" s="79"/>
-      <c r="Q16" s="79"/>
-      <c r="R16" s="79"/>
-      <c r="S16" s="80"/>
-      <c r="T16" s="78">
+      <c r="N16" s="95"/>
+      <c r="O16" s="95"/>
+      <c r="P16" s="95"/>
+      <c r="Q16" s="95"/>
+      <c r="R16" s="95"/>
+      <c r="S16" s="96"/>
+      <c r="T16" s="94">
         <f>SUM(T5:Z15)</f>
         <v>1366</v>
       </c>
-      <c r="U16" s="79"/>
-      <c r="V16" s="79"/>
-      <c r="W16" s="79"/>
-      <c r="X16" s="79"/>
-      <c r="Y16" s="79"/>
-      <c r="Z16" s="80"/>
-      <c r="AA16" s="78">
+      <c r="U16" s="95"/>
+      <c r="V16" s="95"/>
+      <c r="W16" s="95"/>
+      <c r="X16" s="95"/>
+      <c r="Y16" s="95"/>
+      <c r="Z16" s="96"/>
+      <c r="AA16" s="94">
         <f>SUM(AA5:AG15)</f>
         <v>1379</v>
       </c>
-      <c r="AB16" s="79"/>
-      <c r="AC16" s="79"/>
-      <c r="AD16" s="79"/>
-      <c r="AE16" s="79"/>
-      <c r="AF16" s="79"/>
-      <c r="AG16" s="80"/>
+      <c r="AB16" s="95"/>
+      <c r="AC16" s="95"/>
+      <c r="AD16" s="95"/>
+      <c r="AE16" s="95"/>
+      <c r="AF16" s="95"/>
+      <c r="AG16" s="96"/>
       <c r="AH16" s="64"/>
       <c r="AI16" s="53">
         <f>AJ16/31</f>
@@ -5896,146 +5895,153 @@
       </c>
     </row>
     <row r="17" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="81" t="s">
-        <v>25</v>
-      </c>
-      <c r="B17" s="82"/>
-      <c r="C17" s="83"/>
-      <c r="D17" s="84">
+      <c r="A17" s="97" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17" s="97"/>
+      <c r="C17" s="109"/>
+      <c r="D17" s="98">
         <v>9795</v>
       </c>
-      <c r="E17" s="85"/>
-      <c r="F17" s="85"/>
-      <c r="G17" s="85"/>
-      <c r="H17" s="85"/>
-      <c r="I17" s="85"/>
-      <c r="J17" s="85"/>
-      <c r="K17" s="85"/>
-      <c r="L17" s="85"/>
-      <c r="M17" s="85"/>
-      <c r="N17" s="85"/>
-      <c r="O17" s="85"/>
-      <c r="P17" s="85"/>
-      <c r="Q17" s="85"/>
-      <c r="R17" s="85"/>
-      <c r="S17" s="85"/>
-      <c r="T17" s="85"/>
-      <c r="U17" s="85"/>
-      <c r="V17" s="85"/>
-      <c r="W17" s="85"/>
-      <c r="X17" s="85"/>
-      <c r="Y17" s="85"/>
-      <c r="Z17" s="85"/>
-      <c r="AA17" s="85"/>
-      <c r="AB17" s="85"/>
-      <c r="AC17" s="85"/>
-      <c r="AD17" s="85"/>
-      <c r="AE17" s="85"/>
-      <c r="AF17" s="85"/>
-      <c r="AG17" s="85"/>
-      <c r="AH17" s="85"/>
-      <c r="AI17" s="86"/>
-      <c r="AJ17" s="87"/>
-      <c r="AK17" s="71"/>
+      <c r="E17" s="99"/>
+      <c r="F17" s="99"/>
+      <c r="G17" s="99"/>
+      <c r="H17" s="99"/>
+      <c r="I17" s="99"/>
+      <c r="J17" s="99"/>
+      <c r="K17" s="99"/>
+      <c r="L17" s="99"/>
+      <c r="M17" s="99"/>
+      <c r="N17" s="99"/>
+      <c r="O17" s="99"/>
+      <c r="P17" s="99"/>
+      <c r="Q17" s="99"/>
+      <c r="R17" s="99"/>
+      <c r="S17" s="99"/>
+      <c r="T17" s="99"/>
+      <c r="U17" s="99"/>
+      <c r="V17" s="99"/>
+      <c r="W17" s="99"/>
+      <c r="X17" s="99"/>
+      <c r="Y17" s="99"/>
+      <c r="Z17" s="99"/>
+      <c r="AA17" s="99"/>
+      <c r="AB17" s="99"/>
+      <c r="AC17" s="99"/>
+      <c r="AD17" s="99"/>
+      <c r="AE17" s="99"/>
+      <c r="AF17" s="99"/>
+      <c r="AG17" s="99"/>
+      <c r="AH17" s="99"/>
+      <c r="AI17" s="100"/>
+      <c r="AJ17" s="101"/>
+      <c r="AK17" s="69"/>
     </row>
     <row r="18" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="73" t="s">
-        <v>19</v>
-      </c>
-      <c r="B18" s="73"/>
-      <c r="C18" s="74"/>
-      <c r="D18" s="88">
+      <c r="A18" s="89" t="s">
+        <v>27</v>
+      </c>
+      <c r="B18" s="89"/>
+      <c r="C18" s="90"/>
+      <c r="D18" s="102">
         <f>(AJ3+AJ4)-AJ16</f>
         <v>-4219</v>
       </c>
-      <c r="E18" s="86"/>
-      <c r="F18" s="86"/>
-      <c r="G18" s="86"/>
-      <c r="H18" s="86"/>
-      <c r="I18" s="86"/>
-      <c r="J18" s="86"/>
-      <c r="K18" s="86"/>
-      <c r="L18" s="86"/>
-      <c r="M18" s="86"/>
-      <c r="N18" s="86"/>
-      <c r="O18" s="86"/>
-      <c r="P18" s="86"/>
-      <c r="Q18" s="86"/>
-      <c r="R18" s="86"/>
-      <c r="S18" s="86"/>
-      <c r="T18" s="86"/>
-      <c r="U18" s="86"/>
-      <c r="V18" s="86"/>
-      <c r="W18" s="86"/>
-      <c r="X18" s="86"/>
-      <c r="Y18" s="86"/>
-      <c r="Z18" s="86"/>
-      <c r="AA18" s="86"/>
-      <c r="AB18" s="86"/>
-      <c r="AC18" s="86"/>
-      <c r="AD18" s="86"/>
-      <c r="AE18" s="86"/>
-      <c r="AF18" s="86"/>
-      <c r="AG18" s="86"/>
-      <c r="AH18" s="86"/>
-      <c r="AI18" s="86"/>
-      <c r="AJ18" s="87"/>
+      <c r="E18" s="100"/>
+      <c r="F18" s="100"/>
+      <c r="G18" s="100"/>
+      <c r="H18" s="100"/>
+      <c r="I18" s="100"/>
+      <c r="J18" s="100"/>
+      <c r="K18" s="100"/>
+      <c r="L18" s="100"/>
+      <c r="M18" s="100"/>
+      <c r="N18" s="100"/>
+      <c r="O18" s="100"/>
+      <c r="P18" s="100"/>
+      <c r="Q18" s="100"/>
+      <c r="R18" s="100"/>
+      <c r="S18" s="100"/>
+      <c r="T18" s="100"/>
+      <c r="U18" s="100"/>
+      <c r="V18" s="100"/>
+      <c r="W18" s="100"/>
+      <c r="X18" s="100"/>
+      <c r="Y18" s="100"/>
+      <c r="Z18" s="100"/>
+      <c r="AA18" s="100"/>
+      <c r="AB18" s="100"/>
+      <c r="AC18" s="100"/>
+      <c r="AD18" s="100"/>
+      <c r="AE18" s="100"/>
+      <c r="AF18" s="100"/>
+      <c r="AG18" s="100"/>
+      <c r="AH18" s="100"/>
+      <c r="AI18" s="100"/>
+      <c r="AJ18" s="101"/>
       <c r="AK18" s="31">
         <f>((AJ3+AJ4-AJ16)/(AJ3+AJ4))*100</f>
         <v>-843.80000000000007</v>
       </c>
     </row>
     <row r="19" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="72" t="s">
-        <v>26</v>
-      </c>
-      <c r="B19" s="73"/>
-      <c r="C19" s="74"/>
-      <c r="D19" s="75">
+      <c r="A19" s="88" t="s">
+        <v>28</v>
+      </c>
+      <c r="B19" s="89"/>
+      <c r="C19" s="90"/>
+      <c r="D19" s="91">
         <f>(AJ3+AJ4+D17)-AJ16</f>
         <v>5576</v>
       </c>
-      <c r="E19" s="76"/>
-      <c r="F19" s="76"/>
-      <c r="G19" s="76"/>
-      <c r="H19" s="76"/>
-      <c r="I19" s="76"/>
-      <c r="J19" s="76"/>
-      <c r="K19" s="76"/>
-      <c r="L19" s="76"/>
-      <c r="M19" s="76"/>
-      <c r="N19" s="76"/>
-      <c r="O19" s="76"/>
-      <c r="P19" s="76"/>
-      <c r="Q19" s="76"/>
-      <c r="R19" s="76"/>
-      <c r="S19" s="76"/>
-      <c r="T19" s="76"/>
-      <c r="U19" s="76"/>
-      <c r="V19" s="76"/>
-      <c r="W19" s="76"/>
-      <c r="X19" s="76"/>
-      <c r="Y19" s="76"/>
-      <c r="Z19" s="76"/>
-      <c r="AA19" s="76"/>
-      <c r="AB19" s="76"/>
-      <c r="AC19" s="76"/>
-      <c r="AD19" s="76"/>
-      <c r="AE19" s="76"/>
-      <c r="AF19" s="76"/>
-      <c r="AG19" s="76"/>
-      <c r="AH19" s="76"/>
-      <c r="AI19" s="76"/>
-      <c r="AJ19" s="77"/>
+      <c r="E19" s="92"/>
+      <c r="F19" s="92"/>
+      <c r="G19" s="92"/>
+      <c r="H19" s="92"/>
+      <c r="I19" s="92"/>
+      <c r="J19" s="92"/>
+      <c r="K19" s="92"/>
+      <c r="L19" s="92"/>
+      <c r="M19" s="92"/>
+      <c r="N19" s="92"/>
+      <c r="O19" s="92"/>
+      <c r="P19" s="92"/>
+      <c r="Q19" s="92"/>
+      <c r="R19" s="92"/>
+      <c r="S19" s="92"/>
+      <c r="T19" s="92"/>
+      <c r="U19" s="92"/>
+      <c r="V19" s="92"/>
+      <c r="W19" s="92"/>
+      <c r="X19" s="92"/>
+      <c r="Y19" s="92"/>
+      <c r="Z19" s="92"/>
+      <c r="AA19" s="92"/>
+      <c r="AB19" s="92"/>
+      <c r="AC19" s="92"/>
+      <c r="AD19" s="92"/>
+      <c r="AE19" s="92"/>
+      <c r="AF19" s="92"/>
+      <c r="AG19" s="92"/>
+      <c r="AH19" s="92"/>
+      <c r="AI19" s="92"/>
+      <c r="AJ19" s="93"/>
       <c r="AK19" s="54"/>
     </row>
     <row r="24" spans="1:37" x14ac:dyDescent="0.3">
       <c r="S24" s="1" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="21">
+  <mergeCells count="22">
+    <mergeCell ref="A1:C2"/>
+    <mergeCell ref="AI1:AI2"/>
+    <mergeCell ref="AJ1:AJ2"/>
+    <mergeCell ref="AK1:AK2"/>
+    <mergeCell ref="A3:B4"/>
+    <mergeCell ref="AI3:AI4"/>
+    <mergeCell ref="AK3:AK4"/>
     <mergeCell ref="A19:C19"/>
     <mergeCell ref="D19:AJ19"/>
     <mergeCell ref="D16:E16"/>
@@ -6050,13 +6056,7 @@
     <mergeCell ref="A5:A16"/>
     <mergeCell ref="B5:B11"/>
     <mergeCell ref="B12:B15"/>
-    <mergeCell ref="A1:C2"/>
-    <mergeCell ref="AI1:AI2"/>
-    <mergeCell ref="AJ1:AJ2"/>
-    <mergeCell ref="AK1:AK2"/>
-    <mergeCell ref="A3:B4"/>
-    <mergeCell ref="AI3:AI4"/>
-    <mergeCell ref="AK3:AK4"/>
+    <mergeCell ref="B16:C16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
